--- a/catalog.generated.xlsx
+++ b/catalog.generated.xlsx
@@ -598,7 +598,7 @@
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N4" t="str">
         <v/>
@@ -651,7 +651,7 @@
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N5" t="str">
         <v/>
@@ -704,7 +704,7 @@
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N6" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v/>
       </c>
       <c r="M9" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N9" t="str">
         <v/>
@@ -916,7 +916,7 @@
         <v/>
       </c>
       <c r="M10" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N10" t="str">
         <v/>
@@ -969,7 +969,7 @@
         <v/>
       </c>
       <c r="M11" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N11" t="str">
         <v/>
@@ -1022,7 +1022,7 @@
         <v/>
       </c>
       <c r="M12" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N12" t="str">
         <v/>
@@ -1075,7 +1075,7 @@
         <v/>
       </c>
       <c r="M13" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N13" t="str">
         <v/>
@@ -1128,7 +1128,7 @@
         <v/>
       </c>
       <c r="M14" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N14" t="str">
         <v/>
@@ -1181,7 +1181,7 @@
         <v/>
       </c>
       <c r="M15" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N15" t="str">
         <v/>
@@ -1234,7 +1234,7 @@
         <v/>
       </c>
       <c r="M16" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N16" t="str">
         <v/>
@@ -1340,7 +1340,7 @@
         <v/>
       </c>
       <c r="M18" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N18" t="str">
         <v/>
@@ -1393,7 +1393,7 @@
         <v/>
       </c>
       <c r="M19" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N19" t="str">
         <v/>
@@ -1499,7 +1499,7 @@
         <v/>
       </c>
       <c r="M21" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N21" t="str">
         <v/>
@@ -1552,7 +1552,7 @@
         <v/>
       </c>
       <c r="M22" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N22" t="str">
         <v/>
@@ -1605,7 +1605,7 @@
         <v/>
       </c>
       <c r="M23" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N23" t="str">
         <v/>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="M25" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N25" t="str">
         <v/>
@@ -1764,7 +1764,7 @@
         <v/>
       </c>
       <c r="M26" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N26" t="str">
         <v/>
@@ -1817,7 +1817,7 @@
         <v/>
       </c>
       <c r="M27" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N27" t="str">
         <v/>
@@ -1870,7 +1870,7 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="N28" t="str">
         <v/>
@@ -37571,7 +37571,7 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>yes</v>
+        <v/>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -37687,7 +37687,7 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -37774,7 +37774,7 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="H13" t="str">
         <v/>

--- a/catalog.generated.xlsx
+++ b/catalog.generated.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q698"/>
+  <dimension ref="A1:Q711"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -595,7 +595,7 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v/>
+        <v>angle-valve-with-flange-chrome.jpg</v>
       </c>
       <c r="M4" t="str">
         <v/>
@@ -648,7 +648,7 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v/>
+        <v>bath-spout-chrome.jpg</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -704,7 +704,7 @@
         <v/>
       </c>
       <c r="M6" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N6" t="str">
         <v/>
@@ -863,7 +863,7 @@
         <v/>
       </c>
       <c r="M9" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N9" t="str">
         <v/>
@@ -913,7 +913,7 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v/>
+        <v>long-body-with-flange-chrome.jpg</v>
       </c>
       <c r="M10" t="str">
         <v/>
@@ -966,7 +966,7 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v/>
+        <v>nozzle-bib-cock-with-flange-chrome.jpg</v>
       </c>
       <c r="M11" t="str">
         <v/>
@@ -1019,7 +1019,7 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v/>
+        <v>pillar-cock-chrome.jpg</v>
       </c>
       <c r="M12" t="str">
         <v/>
@@ -1075,7 +1075,7 @@
         <v/>
       </c>
       <c r="M13" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N13" t="str">
         <v/>
@@ -1125,7 +1125,7 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v/>
+        <v>single-lever-basin-mixer-chrome.jpg</v>
       </c>
       <c r="M14" t="str">
         <v/>
@@ -1178,7 +1178,7 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v/>
+        <v>single-lever-basin-mixer-extended-body-chrome.jpg</v>
       </c>
       <c r="M15" t="str">
         <v/>
@@ -1231,7 +1231,7 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v/>
+        <v>single-lever-sink-mixer-table-mounted-angular-spout-chrome.jpg</v>
       </c>
       <c r="M16" t="str">
         <v/>
@@ -1340,7 +1340,7 @@
         <v/>
       </c>
       <c r="M18" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N18" t="str">
         <v/>
@@ -1390,7 +1390,7 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>single-lever-sink-mixer-wall-mounted-regular-spout-chrome.jpg</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -1499,7 +1499,7 @@
         <v/>
       </c>
       <c r="M21" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N21" t="str">
         <v/>
@@ -1549,7 +1549,7 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>sink-cock-chrome.jpg</v>
       </c>
       <c r="M22" t="str">
         <v/>
@@ -1602,7 +1602,7 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>sink-mixer-chrome.jpg</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
       <c r="M25" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N25" t="str">
         <v/>
@@ -1764,7 +1764,7 @@
         <v/>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N26" t="str">
         <v/>
@@ -1817,7 +1817,7 @@
         <v/>
       </c>
       <c r="M27" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N27" t="str">
         <v/>
@@ -1870,7 +1870,7 @@
         <v/>
       </c>
       <c r="M28" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N28" t="str">
         <v/>
@@ -34220,22 +34220,22 @@
         <v>Active</v>
       </c>
       <c r="B639" t="str">
-        <v>577-35EXP</v>
+        <v>ST-7014</v>
       </c>
       <c r="C639" t="str">
-        <v>Aliva</v>
+        <v>Single Piece Wc</v>
       </c>
       <c r="D639" t="str">
-        <v>577-35EXP</v>
+        <v>ST-7014</v>
       </c>
       <c r="E639" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>clive-water-closet</v>
       </c>
       <c r="F639" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Clive Water Closet</v>
       </c>
       <c r="G639" t="str">
-        <v>Faucets</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H639" t="str">
         <v/>
@@ -34250,7 +34250,7 @@
         <v/>
       </c>
       <c r="L639" t="str">
-        <v>exposed-parts-for-diverter-35mm-chrome.jpg</v>
+        <v>clive-water-closet-white.png</v>
       </c>
       <c r="M639" t="str">
         <v/>
@@ -34259,13 +34259,13 @@
         <v/>
       </c>
       <c r="O639" t="str">
-        <v>Chrome</v>
+        <v>White</v>
       </c>
       <c r="P639" t="str">
-        <v>Exposed Parts For Diverter in Chrome finish</v>
+        <v>Clive Water Closet in White finish</v>
       </c>
       <c r="Q639" t="str">
-        <v>₹3,023</v>
+        <v>₹12,500</v>
       </c>
     </row>
     <row r="640">
@@ -34273,22 +34273,22 @@
         <v>Active</v>
       </c>
       <c r="B640" t="str">
-        <v>568-15EXP</v>
+        <v>ST-7036</v>
       </c>
       <c r="C640" t="str">
-        <v>Aliva</v>
+        <v>Single Piece Wc</v>
       </c>
       <c r="D640" t="str">
-        <v>568-15EXP</v>
+        <v>ST-7036</v>
       </c>
       <c r="E640" t="str">
-        <v>exposed-parts-for-concealed-stop-cock</v>
+        <v>cinova-water-closet</v>
       </c>
       <c r="F640" t="str">
-        <v>Exposed Parts For Concealed Stop Cock</v>
+        <v>Cinova Water Closet</v>
       </c>
       <c r="G640" t="str">
-        <v>Faucets</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H640" t="str">
         <v/>
@@ -34303,7 +34303,7 @@
         <v/>
       </c>
       <c r="L640" t="str">
-        <v>exposed-parts-for-concealed-stop-cock-1-2-chrome.jpg</v>
+        <v>cinova-water-closet-white.png</v>
       </c>
       <c r="M640" t="str">
         <v/>
@@ -34312,13 +34312,13 @@
         <v/>
       </c>
       <c r="O640" t="str">
-        <v>Chrome</v>
+        <v>White</v>
       </c>
       <c r="P640" t="str">
-        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
+        <v>Cinova Water Closet in White finish</v>
       </c>
       <c r="Q640" t="str">
-        <v>₹1,640</v>
+        <v>₹12,750</v>
       </c>
     </row>
     <row r="641">
@@ -34326,22 +34326,22 @@
         <v>Active</v>
       </c>
       <c r="B641" t="str">
-        <v>AD-3084-S6</v>
+        <v>ST-7027</v>
       </c>
       <c r="C641" t="str">
-        <v>Allied</v>
+        <v>Single Piece Wc</v>
       </c>
       <c r="D641" t="str">
-        <v>AD-3084-S6</v>
+        <v>ST-7027</v>
       </c>
       <c r="E641" t="str">
-        <v>elegant-over-head-shower-square</v>
+        <v>force-water-closet</v>
       </c>
       <c r="F641" t="str">
-        <v>Elegant Over Head Shower Square</v>
+        <v>Force Water Closet</v>
       </c>
       <c r="G641" t="str">
-        <v>Shower</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H641" t="str">
         <v/>
@@ -34356,7 +34356,7 @@
         <v/>
       </c>
       <c r="L641" t="str">
-        <v>elegant-over-head-shower-square-6x6-chrome.jpg</v>
+        <v>force-water-closet-white.png</v>
       </c>
       <c r="M641" t="str">
         <v/>
@@ -34365,13 +34365,13 @@
         <v/>
       </c>
       <c r="O641" t="str">
-        <v>Chrome</v>
+        <v>White</v>
       </c>
       <c r="P641" t="str">
-        <v>Elegant Over Head Shower Square in Chrome finish</v>
+        <v>Force Water Closet in White finish</v>
       </c>
       <c r="Q641" t="str">
-        <v>₹1,540</v>
+        <v>₹13,793</v>
       </c>
     </row>
     <row r="642">
@@ -34379,22 +34379,22 @@
         <v>Active</v>
       </c>
       <c r="B642" t="str">
-        <v>AD-3084-S8-GLD</v>
+        <v>ST-7030</v>
       </c>
       <c r="C642" t="str">
-        <v>Allied</v>
+        <v>Single Piece Wc</v>
       </c>
       <c r="D642" t="str">
-        <v>AD-3084-S6</v>
+        <v>ST-7030</v>
       </c>
       <c r="E642" t="str">
-        <v>elegant-over-head-shower-square</v>
+        <v>glory-water-closet</v>
       </c>
       <c r="F642" t="str">
-        <v>Elegant Over Head Shower Square</v>
+        <v>Glory Water Closet</v>
       </c>
       <c r="G642" t="str">
-        <v>Shower</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H642" t="str">
         <v/>
@@ -34409,7 +34409,7 @@
         <v/>
       </c>
       <c r="L642" t="str">
-        <v>elegant-over-head-shower-square-8x8-rich-gold.png</v>
+        <v>glory-water-closet-white.png</v>
       </c>
       <c r="M642" t="str">
         <v/>
@@ -34418,13 +34418,13 @@
         <v/>
       </c>
       <c r="O642" t="str">
-        <v>Rich Gold</v>
+        <v>White</v>
       </c>
       <c r="P642" t="str">
-        <v>Elegant Over Head Shower Square in Rich Gold finish</v>
+        <v>Glory Water Closet in White finish</v>
       </c>
       <c r="Q642" t="str">
-        <v>₹4,807</v>
+        <v>₹13,933</v>
       </c>
     </row>
     <row r="643">
@@ -34432,22 +34432,22 @@
         <v>Active</v>
       </c>
       <c r="B643" t="str">
-        <v>AD-3084-S8-RGLD</v>
+        <v>ST-7031</v>
       </c>
       <c r="C643" t="str">
-        <v>Allied</v>
+        <v>Single Piece Wc</v>
       </c>
       <c r="D643" t="str">
-        <v>AD-3084-S6</v>
+        <v>ST-7031</v>
       </c>
       <c r="E643" t="str">
-        <v>elegant-over-head-shower-square</v>
+        <v>modenna-water-closet</v>
       </c>
       <c r="F643" t="str">
-        <v>Elegant Over Head Shower Square</v>
+        <v>Modenna Water Closet</v>
       </c>
       <c r="G643" t="str">
-        <v>Shower</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H643" t="str">
         <v/>
@@ -34462,7 +34462,7 @@
         <v/>
       </c>
       <c r="L643" t="str">
-        <v>elegant-over-head-shower-square-8x8-rose-gold.png</v>
+        <v>modenna-water-closet-white.png</v>
       </c>
       <c r="M643" t="str">
         <v/>
@@ -34471,13 +34471,13 @@
         <v/>
       </c>
       <c r="O643" t="str">
-        <v>Rose Gold</v>
+        <v>White</v>
       </c>
       <c r="P643" t="str">
-        <v>Elegant Over Head Shower Square in Rose Gold finish</v>
+        <v>Modenna Water Closet in White finish</v>
       </c>
       <c r="Q643" t="str">
-        <v>₹4,807</v>
+        <v>₹14,488</v>
       </c>
     </row>
     <row r="644">
@@ -34485,22 +34485,22 @@
         <v>Active</v>
       </c>
       <c r="B644" t="str">
-        <v>AD-3047-AL-1</v>
+        <v>ST-7035</v>
       </c>
       <c r="C644" t="str">
-        <v>Allied</v>
+        <v>Single Piece Wc</v>
       </c>
       <c r="D644" t="str">
-        <v>AD-3047-AL-1</v>
+        <v>ST-7035</v>
       </c>
       <c r="E644" t="str">
-        <v>maze-over-head-shower</v>
+        <v>novella-water-closet</v>
       </c>
       <c r="F644" t="str">
-        <v>Maze Over Head Shower</v>
+        <v>Novella Water Closet</v>
       </c>
       <c r="G644" t="str">
-        <v>Shower</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H644" t="str">
         <v/>
@@ -34515,7 +34515,7 @@
         <v/>
       </c>
       <c r="L644" t="str">
-        <v>maze-over-head-shower-4x6-chrome.jpg</v>
+        <v>novella-water-closet-white.png</v>
       </c>
       <c r="M644" t="str">
         <v/>
@@ -34524,13 +34524,13 @@
         <v/>
       </c>
       <c r="O644" t="str">
-        <v>Chrome</v>
+        <v>White</v>
       </c>
       <c r="P644" t="str">
-        <v>Maze Over Head Shower in Chrome finish</v>
+        <v>Novella Water Closet in White finish</v>
       </c>
       <c r="Q644" t="str">
-        <v>₹1,330</v>
+        <v>₹14,488</v>
       </c>
     </row>
     <row r="645">
@@ -34538,22 +34538,22 @@
         <v>Active</v>
       </c>
       <c r="B645" t="str">
-        <v>AD-3048-OV-1</v>
+        <v>ST-7032</v>
       </c>
       <c r="C645" t="str">
-        <v>Allied</v>
+        <v>Single Piece Wc</v>
       </c>
       <c r="D645" t="str">
-        <v>AD-3048-OV-1</v>
+        <v>ST-7032</v>
       </c>
       <c r="E645" t="str">
-        <v>maze-over-head-shower-oval</v>
+        <v>bravet-water-closet</v>
       </c>
       <c r="F645" t="str">
-        <v>Maze Over Head Shower Oval</v>
+        <v>Bravet Water Closet</v>
       </c>
       <c r="G645" t="str">
-        <v>Shower</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H645" t="str">
         <v/>
@@ -34568,7 +34568,7 @@
         <v/>
       </c>
       <c r="L645" t="str">
-        <v>maze-over-head-shower-oval-5x7-chrome.jpg</v>
+        <v>bravet-water-closet-white.png</v>
       </c>
       <c r="M645" t="str">
         <v/>
@@ -34577,13 +34577,13 @@
         <v/>
       </c>
       <c r="O645" t="str">
-        <v>Chrome</v>
+        <v>White</v>
       </c>
       <c r="P645" t="str">
-        <v>Maze Over Head Shower Oval in Chrome finish</v>
+        <v>Bravet Water Closet in White finish</v>
       </c>
       <c r="Q645" t="str">
-        <v>₹1,620</v>
+        <v>₹13,933</v>
       </c>
     </row>
     <row r="646">
@@ -34591,22 +34591,22 @@
         <v>Active</v>
       </c>
       <c r="B646" t="str">
-        <v>AD-3003</v>
+        <v>ST-4024</v>
       </c>
       <c r="C646" t="str">
-        <v>Allied</v>
+        <v>Wall Hung Wc</v>
       </c>
       <c r="D646" t="str">
-        <v>AD-3003</v>
+        <v>ST-4024</v>
       </c>
       <c r="E646" t="str">
-        <v>maze-over-head-shower-square</v>
+        <v>wall-hung-rimless-modenna</v>
       </c>
       <c r="F646" t="str">
-        <v>Maze Over Head Shower Square</v>
+        <v>Wall Hung Rimless Modenna</v>
       </c>
       <c r="G646" t="str">
-        <v>Shower</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H646" t="str">
         <v/>
@@ -34621,7 +34621,7 @@
         <v/>
       </c>
       <c r="L646" t="str">
-        <v>maze-over-head-shower-square-4x4-chrome.jpg</v>
+        <v>wall-hung-rimless-modenna-white.png</v>
       </c>
       <c r="M646" t="str">
         <v/>
@@ -34630,13 +34630,13 @@
         <v/>
       </c>
       <c r="O646" t="str">
-        <v>Chrome</v>
+        <v>White</v>
       </c>
       <c r="P646" t="str">
-        <v>Maze Over Head Shower Square in Chrome finish</v>
+        <v>Wall Hung Rimless Modenna in White finish</v>
       </c>
       <c r="Q646" t="str">
-        <v>₹1,050</v>
+        <v>₹13,613</v>
       </c>
     </row>
     <row r="647">
@@ -34644,22 +34644,22 @@
         <v>Active</v>
       </c>
       <c r="B647" t="str">
-        <v>AD-3000-GMB</v>
+        <v>ST-4023</v>
       </c>
       <c r="C647" t="str">
-        <v>Allied</v>
+        <v>Wall Hung Wc</v>
       </c>
       <c r="D647" t="str">
-        <v>AD-3003</v>
+        <v>ST-4023</v>
       </c>
       <c r="E647" t="str">
-        <v>maze-over-head-shower-square</v>
+        <v>wall-hung-rimless-novella</v>
       </c>
       <c r="F647" t="str">
-        <v>Maze Over Head Shower Square</v>
+        <v>Wall Hung Rimless Novella</v>
       </c>
       <c r="G647" t="str">
-        <v>Shower</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H647" t="str">
         <v/>
@@ -34674,7 +34674,7 @@
         <v/>
       </c>
       <c r="L647" t="str">
-        <v>maze-over-head-shower-square-6x6-gunmetal-black.png</v>
+        <v>wall-hung-rimless-novella-white.png</v>
       </c>
       <c r="M647" t="str">
         <v/>
@@ -34683,13 +34683,13 @@
         <v/>
       </c>
       <c r="O647" t="str">
-        <v>Gunmetal Black</v>
+        <v>White</v>
       </c>
       <c r="P647" t="str">
-        <v>Maze Over Head Shower Square in Gunmetal Black finish</v>
+        <v>Wall Hung Rimless Novella in White finish</v>
       </c>
       <c r="Q647" t="str">
-        <v/>
+        <v>₹13,095</v>
       </c>
     </row>
     <row r="648">
@@ -34697,22 +34697,22 @@
         <v>Active</v>
       </c>
       <c r="B648" t="str">
-        <v>AD-3000-GMBG</v>
+        <v>ST-1014</v>
       </c>
       <c r="C648" t="str">
-        <v>Allied</v>
+        <v>Basin With Pedestal</v>
       </c>
       <c r="D648" t="str">
-        <v>AD-3003</v>
+        <v>ST-1014</v>
       </c>
       <c r="E648" t="str">
-        <v>maze-over-head-shower-square</v>
+        <v>wash-basin-with-pedestal-neo</v>
       </c>
       <c r="F648" t="str">
-        <v>Maze Over Head Shower Square</v>
+        <v>Wash Basin with Pedestal Neo</v>
       </c>
       <c r="G648" t="str">
-        <v>Shower</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H648" t="str">
         <v/>
@@ -34727,7 +34727,7 @@
         <v/>
       </c>
       <c r="L648" t="str">
-        <v>maze-over-head-shower-square-6x6-gunmetal-black-gold.png</v>
+        <v>wash-basin-with-pedestal-neo-white.png</v>
       </c>
       <c r="M648" t="str">
         <v/>
@@ -34736,13 +34736,13 @@
         <v/>
       </c>
       <c r="O648" t="str">
-        <v>Gunmetal Black Gold</v>
+        <v>White</v>
       </c>
       <c r="P648" t="str">
-        <v>Maze Over Head Shower Square in Gunmetal Black Gold finish</v>
+        <v>Wash Basin with Pedestal Neo in White finish</v>
       </c>
       <c r="Q648" t="str">
-        <v/>
+        <v>₹3,646</v>
       </c>
     </row>
     <row r="649">
@@ -34750,22 +34750,22 @@
         <v>Active</v>
       </c>
       <c r="B649" t="str">
-        <v>AD-3000-MB</v>
+        <v>ST-1015</v>
       </c>
       <c r="C649" t="str">
-        <v>Allied</v>
+        <v>Basin With Pedestal</v>
       </c>
       <c r="D649" t="str">
-        <v>AD-3003</v>
+        <v>ST-1015</v>
       </c>
       <c r="E649" t="str">
-        <v>maze-over-head-shower-square</v>
+        <v>wash-basin-with-pedestal-cocoon</v>
       </c>
       <c r="F649" t="str">
-        <v>Maze Over Head Shower Square</v>
+        <v>Wash Basin with Pedestal Cocoon</v>
       </c>
       <c r="G649" t="str">
-        <v>Shower</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H649" t="str">
         <v/>
@@ -34780,7 +34780,7 @@
         <v/>
       </c>
       <c r="L649" t="str">
-        <v>maze-over-head-shower-square-6x6-matt-black.png</v>
+        <v>wash-basin-with-pedestal-cocoon-white.png</v>
       </c>
       <c r="M649" t="str">
         <v/>
@@ -34789,13 +34789,13 @@
         <v/>
       </c>
       <c r="O649" t="str">
-        <v>Matt Black</v>
+        <v>White</v>
       </c>
       <c r="P649" t="str">
-        <v>Maze Over Head Shower Square in Matt Black finish</v>
+        <v>Wash Basin with Pedestal Cocoon in White finish</v>
       </c>
       <c r="Q649" t="str">
-        <v/>
+        <v>₹3,308</v>
       </c>
     </row>
     <row r="650">
@@ -34803,22 +34803,22 @@
         <v>Active</v>
       </c>
       <c r="B650" t="str">
-        <v>AD-3000-MBG</v>
+        <v>ST-3012</v>
       </c>
       <c r="C650" t="str">
-        <v>Allied</v>
+        <v>Basin With Pedestal</v>
       </c>
       <c r="D650" t="str">
-        <v>AD-3003</v>
+        <v>ST-3012</v>
       </c>
       <c r="E650" t="str">
-        <v>maze-over-head-shower-square</v>
+        <v>wash-basin-with-pedestal-cargo</v>
       </c>
       <c r="F650" t="str">
-        <v>Maze Over Head Shower Square</v>
+        <v>Wash Basin with Pedestal Cargo</v>
       </c>
       <c r="G650" t="str">
-        <v>Shower</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H650" t="str">
         <v/>
@@ -34833,7 +34833,7 @@
         <v/>
       </c>
       <c r="L650" t="str">
-        <v>maze-over-head-shower-square-6x6-matt-black-gold.png</v>
+        <v>wash-basin-with-pedestal-cargo-white.png</v>
       </c>
       <c r="M650" t="str">
         <v/>
@@ -34842,13 +34842,13 @@
         <v/>
       </c>
       <c r="O650" t="str">
-        <v>Matt Black Gold</v>
+        <v>White</v>
       </c>
       <c r="P650" t="str">
-        <v>Maze Over Head Shower Square in Matt Black Gold finish</v>
+        <v>Wash Basin with Pedestal Cargo in White finish</v>
       </c>
       <c r="Q650" t="str">
-        <v/>
+        <v>₹3,050</v>
       </c>
     </row>
     <row r="651">
@@ -34856,22 +34856,22 @@
         <v>Active</v>
       </c>
       <c r="B651" t="str">
-        <v>AD-3000-MW</v>
+        <v>ST-1007</v>
       </c>
       <c r="C651" t="str">
-        <v>Allied</v>
+        <v>Basin With Pedestal</v>
       </c>
       <c r="D651" t="str">
-        <v>AD-3003</v>
+        <v>ST-1007</v>
       </c>
       <c r="E651" t="str">
-        <v>maze-over-head-shower-square</v>
+        <v>wash-basin-with-pedestal-belleza</v>
       </c>
       <c r="F651" t="str">
-        <v>Maze Over Head Shower Square</v>
+        <v>Wash Basin with Pedestal Belleza</v>
       </c>
       <c r="G651" t="str">
-        <v>Shower</v>
+        <v>Sanitaryware</v>
       </c>
       <c r="H651" t="str">
         <v/>
@@ -34886,7 +34886,7 @@
         <v/>
       </c>
       <c r="L651" t="str">
-        <v>maze-over-head-shower-square-6x6-matt-white.png</v>
+        <v>wash-basin-with-pedestal-belleza-white.png</v>
       </c>
       <c r="M651" t="str">
         <v/>
@@ -34895,13 +34895,13 @@
         <v/>
       </c>
       <c r="O651" t="str">
-        <v>Matt White</v>
+        <v>White</v>
       </c>
       <c r="P651" t="str">
-        <v>Maze Over Head Shower Square in Matt White finish</v>
+        <v>Wash Basin with Pedestal Belleza in White finish</v>
       </c>
       <c r="Q651" t="str">
-        <v/>
+        <v>₹3,866</v>
       </c>
     </row>
     <row r="652">
@@ -34909,22 +34909,22 @@
         <v>Active</v>
       </c>
       <c r="B652" t="str">
-        <v>AD-3000-MWG</v>
+        <v>577-35EXP</v>
       </c>
       <c r="C652" t="str">
-        <v>Allied</v>
+        <v>Aliva</v>
       </c>
       <c r="D652" t="str">
-        <v>AD-3003</v>
+        <v>577-35EXP</v>
       </c>
       <c r="E652" t="str">
-        <v>maze-over-head-shower-square</v>
+        <v>exposed-parts-for-diverter</v>
       </c>
       <c r="F652" t="str">
-        <v>Maze Over Head Shower Square</v>
+        <v>Exposed Parts For Diverter</v>
       </c>
       <c r="G652" t="str">
-        <v>Shower</v>
+        <v>Faucets</v>
       </c>
       <c r="H652" t="str">
         <v/>
@@ -34939,22 +34939,22 @@
         <v/>
       </c>
       <c r="L652" t="str">
-        <v>maze-over-head-shower-square-6x6-matt-white-gold.png</v>
+        <v/>
       </c>
       <c r="M652" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N652" t="str">
         <v/>
       </c>
       <c r="O652" t="str">
-        <v>Matt White Gold</v>
+        <v>Chrome</v>
       </c>
       <c r="P652" t="str">
-        <v>Maze Over Head Shower Square in Matt White Gold finish</v>
+        <v>Exposed Parts For Diverter in Chrome finish</v>
       </c>
       <c r="Q652" t="str">
-        <v/>
+        <v>₹3,023</v>
       </c>
     </row>
     <row r="653">
@@ -34962,22 +34962,22 @@
         <v>Active</v>
       </c>
       <c r="B653" t="str">
-        <v>AD-3000-MBE</v>
+        <v>568-15EXP</v>
       </c>
       <c r="C653" t="str">
-        <v>Allied</v>
+        <v>Aliva</v>
       </c>
       <c r="D653" t="str">
-        <v>AD-3003</v>
+        <v>568-15EXP</v>
       </c>
       <c r="E653" t="str">
-        <v>maze-over-head-shower-square</v>
+        <v>exposed-parts-for-concealed-stop-cock</v>
       </c>
       <c r="F653" t="str">
-        <v>Maze Over Head Shower Square</v>
+        <v>Exposed Parts For Concealed Stop Cock</v>
       </c>
       <c r="G653" t="str">
-        <v>Shower</v>
+        <v>Faucets</v>
       </c>
       <c r="H653" t="str">
         <v/>
@@ -34992,22 +34992,22 @@
         <v/>
       </c>
       <c r="L653" t="str">
-        <v>maze-over-head-shower-square-6x6-matt-beige.png</v>
+        <v/>
       </c>
       <c r="M653" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N653" t="str">
         <v/>
       </c>
       <c r="O653" t="str">
-        <v>Matt Beige</v>
+        <v>Chrome</v>
       </c>
       <c r="P653" t="str">
-        <v>Maze Over Head Shower Square in Matt Beige finish</v>
+        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
       </c>
       <c r="Q653" t="str">
-        <v/>
+        <v>₹1,640</v>
       </c>
     </row>
     <row r="654">
@@ -35015,19 +35015,19 @@
         <v>Active</v>
       </c>
       <c r="B654" t="str">
-        <v>AD-3000-MBEG</v>
+        <v>AD-3084-S6</v>
       </c>
       <c r="C654" t="str">
         <v>Allied</v>
       </c>
       <c r="D654" t="str">
-        <v>AD-3003</v>
+        <v>AD-3084-S6</v>
       </c>
       <c r="E654" t="str">
-        <v>maze-over-head-shower-square</v>
+        <v>elegant-over-head-shower-square</v>
       </c>
       <c r="F654" t="str">
-        <v>Maze Over Head Shower Square</v>
+        <v>Elegant Over Head Shower Square</v>
       </c>
       <c r="G654" t="str">
         <v>Shower</v>
@@ -35045,22 +35045,22 @@
         <v/>
       </c>
       <c r="L654" t="str">
-        <v>maze-over-head-shower-square-6x6-matt-beige-gold.png</v>
+        <v/>
       </c>
       <c r="M654" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N654" t="str">
         <v/>
       </c>
       <c r="O654" t="str">
-        <v>Matt Beige Gold</v>
+        <v>Chrome</v>
       </c>
       <c r="P654" t="str">
-        <v>Maze Over Head Shower Square in Matt Beige Gold finish</v>
+        <v>Elegant Over Head Shower Square in Chrome finish</v>
       </c>
       <c r="Q654" t="str">
-        <v/>
+        <v>₹1,540</v>
       </c>
     </row>
     <row r="655">
@@ -35068,19 +35068,19 @@
         <v>Active</v>
       </c>
       <c r="B655" t="str">
-        <v>AD-3000-MGR</v>
+        <v>AD-3084-S8-GLD</v>
       </c>
       <c r="C655" t="str">
         <v>Allied</v>
       </c>
       <c r="D655" t="str">
-        <v>AD-3003</v>
+        <v>AD-3084-S6</v>
       </c>
       <c r="E655" t="str">
-        <v>maze-over-head-shower-square</v>
+        <v>elegant-over-head-shower-square</v>
       </c>
       <c r="F655" t="str">
-        <v>Maze Over Head Shower Square</v>
+        <v>Elegant Over Head Shower Square</v>
       </c>
       <c r="G655" t="str">
         <v>Shower</v>
@@ -35098,22 +35098,22 @@
         <v/>
       </c>
       <c r="L655" t="str">
-        <v>maze-over-head-shower-square-6x6-matt-grey.png</v>
+        <v/>
       </c>
       <c r="M655" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N655" t="str">
         <v/>
       </c>
       <c r="O655" t="str">
-        <v>Matt Grey</v>
+        <v>Rich Gold</v>
       </c>
       <c r="P655" t="str">
-        <v>Maze Over Head Shower Square in Matt Grey finish</v>
+        <v>Elegant Over Head Shower Square in Rich Gold finish</v>
       </c>
       <c r="Q655" t="str">
-        <v/>
+        <v>₹4,807</v>
       </c>
     </row>
     <row r="656">
@@ -35121,19 +35121,19 @@
         <v>Active</v>
       </c>
       <c r="B656" t="str">
-        <v>AD-3000-MGRG</v>
+        <v>AD-3084-S8-RGLD</v>
       </c>
       <c r="C656" t="str">
         <v>Allied</v>
       </c>
       <c r="D656" t="str">
-        <v>AD-3003</v>
+        <v>AD-3084-S6</v>
       </c>
       <c r="E656" t="str">
-        <v>maze-over-head-shower-square</v>
+        <v>elegant-over-head-shower-square</v>
       </c>
       <c r="F656" t="str">
-        <v>Maze Over Head Shower Square</v>
+        <v>Elegant Over Head Shower Square</v>
       </c>
       <c r="G656" t="str">
         <v>Shower</v>
@@ -35151,22 +35151,22 @@
         <v/>
       </c>
       <c r="L656" t="str">
-        <v>maze-over-head-shower-square-6x6-matt-grey-gold.png</v>
+        <v/>
       </c>
       <c r="M656" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N656" t="str">
         <v/>
       </c>
       <c r="O656" t="str">
-        <v>Matt Grey Gold</v>
+        <v>Rose Gold</v>
       </c>
       <c r="P656" t="str">
-        <v>Maze Over Head Shower Square in Matt Grey Gold finish</v>
+        <v>Elegant Over Head Shower Square in Rose Gold finish</v>
       </c>
       <c r="Q656" t="str">
-        <v/>
+        <v>₹4,807</v>
       </c>
     </row>
     <row r="657">
@@ -35174,22 +35174,22 @@
         <v>Active</v>
       </c>
       <c r="B657" t="str">
-        <v>AD-3051</v>
+        <v>AD-3047-AL-1</v>
       </c>
       <c r="C657" t="str">
         <v>Allied</v>
       </c>
       <c r="D657" t="str">
-        <v>AD-3051</v>
+        <v>AD-3047-AL-1</v>
       </c>
       <c r="E657" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower</v>
       </c>
       <c r="F657" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower</v>
       </c>
       <c r="G657" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H657" t="str">
         <v/>
@@ -35204,10 +35204,10 @@
         <v/>
       </c>
       <c r="L657" t="str">
-        <v>shower-arm-round-9-chrome.png</v>
+        <v/>
       </c>
       <c r="M657" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N657" t="str">
         <v/>
@@ -35216,10 +35216,10 @@
         <v>Chrome</v>
       </c>
       <c r="P657" t="str">
-        <v>Shower Arm Round in Chrome finish</v>
+        <v>Maze Over Head Shower in Chrome finish</v>
       </c>
       <c r="Q657" t="str">
-        <v>₹801</v>
+        <v>₹1,330</v>
       </c>
     </row>
     <row r="658">
@@ -35227,22 +35227,22 @@
         <v>Active</v>
       </c>
       <c r="B658" t="str">
-        <v>AD-3053-GLD</v>
+        <v>AD-3048-OV-1</v>
       </c>
       <c r="C658" t="str">
         <v>Allied</v>
       </c>
       <c r="D658" t="str">
-        <v>AD-3051</v>
+        <v>AD-3048-OV-1</v>
       </c>
       <c r="E658" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower-oval</v>
       </c>
       <c r="F658" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower Oval</v>
       </c>
       <c r="G658" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H658" t="str">
         <v/>
@@ -35257,22 +35257,22 @@
         <v/>
       </c>
       <c r="L658" t="str">
-        <v>shower-arm-round-18-rich-gold.png</v>
+        <v/>
       </c>
       <c r="M658" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N658" t="str">
         <v/>
       </c>
       <c r="O658" t="str">
-        <v>Rich Gold</v>
+        <v>Chrome</v>
       </c>
       <c r="P658" t="str">
-        <v>Shower Arm Round in Rich Gold finish</v>
+        <v>Maze Over Head Shower Oval in Chrome finish</v>
       </c>
       <c r="Q658" t="str">
-        <v>₹2,992</v>
+        <v>₹1,620</v>
       </c>
     </row>
     <row r="659">
@@ -35280,22 +35280,22 @@
         <v>Active</v>
       </c>
       <c r="B659" t="str">
-        <v>AD-3053-RGLD</v>
+        <v>AD-3003</v>
       </c>
       <c r="C659" t="str">
         <v>Allied</v>
       </c>
       <c r="D659" t="str">
-        <v>AD-3051</v>
+        <v>AD-3003</v>
       </c>
       <c r="E659" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower-square</v>
       </c>
       <c r="F659" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower Square</v>
       </c>
       <c r="G659" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H659" t="str">
         <v/>
@@ -35310,22 +35310,22 @@
         <v/>
       </c>
       <c r="L659" t="str">
-        <v>shower-arm-round-18-rose-gold.png</v>
+        <v/>
       </c>
       <c r="M659" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N659" t="str">
         <v/>
       </c>
       <c r="O659" t="str">
-        <v>Rose Gold</v>
+        <v>Chrome</v>
       </c>
       <c r="P659" t="str">
-        <v>Shower Arm Round in Rose Gold finish</v>
+        <v>Maze Over Head Shower Square in Chrome finish</v>
       </c>
       <c r="Q659" t="str">
-        <v>₹2,992</v>
+        <v>₹1,050</v>
       </c>
     </row>
     <row r="660">
@@ -35333,22 +35333,22 @@
         <v>Active</v>
       </c>
       <c r="B660" t="str">
-        <v>AD-3053-GMB</v>
+        <v>AD-3000-GMB</v>
       </c>
       <c r="C660" t="str">
         <v>Allied</v>
       </c>
       <c r="D660" t="str">
-        <v>AD-3051</v>
+        <v>AD-3003</v>
       </c>
       <c r="E660" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower-square</v>
       </c>
       <c r="F660" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower Square</v>
       </c>
       <c r="G660" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H660" t="str">
         <v/>
@@ -35366,7 +35366,7 @@
         <v/>
       </c>
       <c r="M660" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N660" t="str">
         <v/>
@@ -35375,10 +35375,10 @@
         <v>Gunmetal Black</v>
       </c>
       <c r="P660" t="str">
-        <v>Shower Arm Round in Gunmetal Black finish</v>
+        <v>Maze Over Head Shower Square in Gunmetal Black finish</v>
       </c>
       <c r="Q660" t="str">
-        <v>₹1,601</v>
+        <v/>
       </c>
     </row>
     <row r="661">
@@ -35386,22 +35386,22 @@
         <v>Active</v>
       </c>
       <c r="B661" t="str">
-        <v>AD-3053-GMBG</v>
+        <v>AD-3000-GMBG</v>
       </c>
       <c r="C661" t="str">
         <v>Allied</v>
       </c>
       <c r="D661" t="str">
-        <v>AD-3051</v>
+        <v>AD-3003</v>
       </c>
       <c r="E661" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower-square</v>
       </c>
       <c r="F661" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower Square</v>
       </c>
       <c r="G661" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H661" t="str">
         <v/>
@@ -35419,7 +35419,7 @@
         <v/>
       </c>
       <c r="M661" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N661" t="str">
         <v/>
@@ -35428,10 +35428,10 @@
         <v>Gunmetal Black Gold</v>
       </c>
       <c r="P661" t="str">
-        <v>Shower Arm Round in Gunmetal Black Gold finish</v>
+        <v>Maze Over Head Shower Square in Gunmetal Black Gold finish</v>
       </c>
       <c r="Q661" t="str">
-        <v>₹1,782</v>
+        <v/>
       </c>
     </row>
     <row r="662">
@@ -35439,22 +35439,22 @@
         <v>Active</v>
       </c>
       <c r="B662" t="str">
-        <v>AD-3053-MB</v>
+        <v>AD-3000-MB</v>
       </c>
       <c r="C662" t="str">
         <v>Allied</v>
       </c>
       <c r="D662" t="str">
-        <v>AD-3051</v>
+        <v>AD-3003</v>
       </c>
       <c r="E662" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower-square</v>
       </c>
       <c r="F662" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower Square</v>
       </c>
       <c r="G662" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H662" t="str">
         <v/>
@@ -35469,10 +35469,10 @@
         <v/>
       </c>
       <c r="L662" t="str">
-        <v>shower-arm-round-18-matt-black.png</v>
+        <v/>
       </c>
       <c r="M662" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N662" t="str">
         <v/>
@@ -35481,10 +35481,10 @@
         <v>Matt Black</v>
       </c>
       <c r="P662" t="str">
-        <v>Shower Arm Round in Matt Black finish</v>
+        <v>Maze Over Head Shower Square in Matt Black finish</v>
       </c>
       <c r="Q662" t="str">
-        <v>₹1,601</v>
+        <v/>
       </c>
     </row>
     <row r="663">
@@ -35492,22 +35492,22 @@
         <v>Active</v>
       </c>
       <c r="B663" t="str">
-        <v>AD-3053-MBG</v>
+        <v>AD-3000-MBG</v>
       </c>
       <c r="C663" t="str">
         <v>Allied</v>
       </c>
       <c r="D663" t="str">
-        <v>AD-3051</v>
+        <v>AD-3003</v>
       </c>
       <c r="E663" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower-square</v>
       </c>
       <c r="F663" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower Square</v>
       </c>
       <c r="G663" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H663" t="str">
         <v/>
@@ -35522,10 +35522,10 @@
         <v/>
       </c>
       <c r="L663" t="str">
-        <v>shower-arm-round-18-matt-black-gold.jpg</v>
+        <v/>
       </c>
       <c r="M663" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N663" t="str">
         <v/>
@@ -35534,10 +35534,10 @@
         <v>Matt Black Gold</v>
       </c>
       <c r="P663" t="str">
-        <v>Shower Arm Round in Matt Black Gold finish</v>
+        <v>Maze Over Head Shower Square in Matt Black Gold finish</v>
       </c>
       <c r="Q663" t="str">
-        <v>₹1,782</v>
+        <v/>
       </c>
     </row>
     <row r="664">
@@ -35545,22 +35545,22 @@
         <v>Active</v>
       </c>
       <c r="B664" t="str">
-        <v>AD-3053-MW</v>
+        <v>AD-3000-MW</v>
       </c>
       <c r="C664" t="str">
         <v>Allied</v>
       </c>
       <c r="D664" t="str">
-        <v>AD-3051</v>
+        <v>AD-3003</v>
       </c>
       <c r="E664" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower-square</v>
       </c>
       <c r="F664" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower Square</v>
       </c>
       <c r="G664" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H664" t="str">
         <v/>
@@ -35575,10 +35575,10 @@
         <v/>
       </c>
       <c r="L664" t="str">
-        <v>shower-arm-round-18-matt-white.png</v>
+        <v/>
       </c>
       <c r="M664" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N664" t="str">
         <v/>
@@ -35587,10 +35587,10 @@
         <v>Matt White</v>
       </c>
       <c r="P664" t="str">
-        <v>Shower Arm Round in Matt White finish</v>
+        <v>Maze Over Head Shower Square in Matt White finish</v>
       </c>
       <c r="Q664" t="str">
-        <v>₹1,601</v>
+        <v/>
       </c>
     </row>
     <row r="665">
@@ -35598,22 +35598,22 @@
         <v>Active</v>
       </c>
       <c r="B665" t="str">
-        <v>AD-3053-MWG</v>
+        <v>AD-3000-MWG</v>
       </c>
       <c r="C665" t="str">
         <v>Allied</v>
       </c>
       <c r="D665" t="str">
-        <v>AD-3051</v>
+        <v>AD-3003</v>
       </c>
       <c r="E665" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower-square</v>
       </c>
       <c r="F665" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower Square</v>
       </c>
       <c r="G665" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H665" t="str">
         <v/>
@@ -35628,10 +35628,10 @@
         <v/>
       </c>
       <c r="L665" t="str">
-        <v>shower-arm-round-18-matt-white-gold.png</v>
+        <v/>
       </c>
       <c r="M665" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N665" t="str">
         <v/>
@@ -35640,10 +35640,10 @@
         <v>Matt White Gold</v>
       </c>
       <c r="P665" t="str">
-        <v>Shower Arm Round in Matt White Gold finish</v>
+        <v>Maze Over Head Shower Square in Matt White Gold finish</v>
       </c>
       <c r="Q665" t="str">
-        <v>₹1,782</v>
+        <v/>
       </c>
     </row>
     <row r="666">
@@ -35651,22 +35651,22 @@
         <v>Active</v>
       </c>
       <c r="B666" t="str">
-        <v>AD-3053-MBE</v>
+        <v>AD-3000-MBE</v>
       </c>
       <c r="C666" t="str">
         <v>Allied</v>
       </c>
       <c r="D666" t="str">
-        <v>AD-3051</v>
+        <v>AD-3003</v>
       </c>
       <c r="E666" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower-square</v>
       </c>
       <c r="F666" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower Square</v>
       </c>
       <c r="G666" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H666" t="str">
         <v/>
@@ -35681,10 +35681,10 @@
         <v/>
       </c>
       <c r="L666" t="str">
-        <v>shower-arm-round-18-matt-beige.png</v>
+        <v/>
       </c>
       <c r="M666" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N666" t="str">
         <v/>
@@ -35693,10 +35693,10 @@
         <v>Matt Beige</v>
       </c>
       <c r="P666" t="str">
-        <v>Shower Arm Round in Matt Beige finish</v>
+        <v>Maze Over Head Shower Square in Matt Beige finish</v>
       </c>
       <c r="Q666" t="str">
-        <v>₹1,601</v>
+        <v/>
       </c>
     </row>
     <row r="667">
@@ -35704,22 +35704,22 @@
         <v>Active</v>
       </c>
       <c r="B667" t="str">
-        <v>AD-3053-MBEG</v>
+        <v>AD-3000-MBEG</v>
       </c>
       <c r="C667" t="str">
         <v>Allied</v>
       </c>
       <c r="D667" t="str">
-        <v>AD-3051</v>
+        <v>AD-3003</v>
       </c>
       <c r="E667" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower-square</v>
       </c>
       <c r="F667" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower Square</v>
       </c>
       <c r="G667" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H667" t="str">
         <v/>
@@ -35734,10 +35734,10 @@
         <v/>
       </c>
       <c r="L667" t="str">
-        <v>shower-arm-round-18-matt-beige-gold.png</v>
+        <v/>
       </c>
       <c r="M667" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N667" t="str">
         <v/>
@@ -35746,10 +35746,10 @@
         <v>Matt Beige Gold</v>
       </c>
       <c r="P667" t="str">
-        <v>Shower Arm Round in Matt Beige Gold finish</v>
+        <v>Maze Over Head Shower Square in Matt Beige Gold finish</v>
       </c>
       <c r="Q667" t="str">
-        <v>₹1,782</v>
+        <v/>
       </c>
     </row>
     <row r="668">
@@ -35757,22 +35757,22 @@
         <v>Active</v>
       </c>
       <c r="B668" t="str">
-        <v>AD-3053-MGR</v>
+        <v>AD-3000-MGR</v>
       </c>
       <c r="C668" t="str">
         <v>Allied</v>
       </c>
       <c r="D668" t="str">
-        <v>AD-3051</v>
+        <v>AD-3003</v>
       </c>
       <c r="E668" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower-square</v>
       </c>
       <c r="F668" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower Square</v>
       </c>
       <c r="G668" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H668" t="str">
         <v/>
@@ -35787,10 +35787,10 @@
         <v/>
       </c>
       <c r="L668" t="str">
-        <v>shower-arm-round-18-matt-grey.png</v>
+        <v/>
       </c>
       <c r="M668" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N668" t="str">
         <v/>
@@ -35799,10 +35799,10 @@
         <v>Matt Grey</v>
       </c>
       <c r="P668" t="str">
-        <v>Shower Arm Round in Matt Grey finish</v>
+        <v>Maze Over Head Shower Square in Matt Grey finish</v>
       </c>
       <c r="Q668" t="str">
-        <v>₹1,601</v>
+        <v/>
       </c>
     </row>
     <row r="669">
@@ -35810,22 +35810,22 @@
         <v>Active</v>
       </c>
       <c r="B669" t="str">
-        <v>AD-3053-MGRG</v>
+        <v>AD-3000-MGRG</v>
       </c>
       <c r="C669" t="str">
         <v>Allied</v>
       </c>
       <c r="D669" t="str">
-        <v>AD-3051</v>
+        <v>AD-3003</v>
       </c>
       <c r="E669" t="str">
-        <v>shower-arm-round</v>
+        <v>maze-over-head-shower-square</v>
       </c>
       <c r="F669" t="str">
-        <v>Shower Arm Round</v>
+        <v>Maze Over Head Shower Square</v>
       </c>
       <c r="G669" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H669" t="str">
         <v/>
@@ -35840,10 +35840,10 @@
         <v/>
       </c>
       <c r="L669" t="str">
-        <v>shower-arm-round-18-matt-grey-gold.png</v>
+        <v/>
       </c>
       <c r="M669" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N669" t="str">
         <v/>
@@ -35852,10 +35852,10 @@
         <v>Matt Grey Gold</v>
       </c>
       <c r="P669" t="str">
-        <v>Shower Arm Round in Matt Grey Gold finish</v>
+        <v>Maze Over Head Shower Square in Matt Grey Gold finish</v>
       </c>
       <c r="Q669" t="str">
-        <v>₹1,782</v>
+        <v/>
       </c>
     </row>
     <row r="670">
@@ -35863,22 +35863,22 @@
         <v>Active</v>
       </c>
       <c r="B670" t="str">
-        <v>AD-3071</v>
+        <v>AD-3051</v>
       </c>
       <c r="C670" t="str">
         <v>Allied</v>
       </c>
       <c r="D670" t="str">
-        <v>AD-3071</v>
+        <v>AD-3051</v>
       </c>
       <c r="E670" t="str">
-        <v>ultra-slim-over-head-shower-square</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F670" t="str">
-        <v>Ultra Slim Over Head Shower Square</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G670" t="str">
-        <v>Shower</v>
+        <v>Faucets</v>
       </c>
       <c r="H670" t="str">
         <v/>
@@ -35893,10 +35893,10 @@
         <v/>
       </c>
       <c r="L670" t="str">
-        <v>ultra-slim-over-head-shower-square-4x4-chrome.jpg</v>
+        <v/>
       </c>
       <c r="M670" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N670" t="str">
         <v/>
@@ -35905,10 +35905,10 @@
         <v>Chrome</v>
       </c>
       <c r="P670" t="str">
-        <v>Ultra Slim Over Head Shower Square in Chrome finish</v>
+        <v>Shower Arm Round in Chrome finish</v>
       </c>
       <c r="Q670" t="str">
-        <v>₹625</v>
+        <v>₹801</v>
       </c>
     </row>
     <row r="671">
@@ -35916,19 +35916,19 @@
         <v>Active</v>
       </c>
       <c r="B671" t="str">
-        <v>1810-15EXP</v>
+        <v>AD-3053-GLD</v>
       </c>
       <c r="C671" t="str">
-        <v>Cube Prima</v>
+        <v>Allied</v>
       </c>
       <c r="D671" t="str">
-        <v>1810-15EXP</v>
+        <v>AD-3051</v>
       </c>
       <c r="E671" t="str">
-        <v>exposed-parts-for-concealed-stop-cock</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F671" t="str">
-        <v>Exposed Parts For Concealed Stop Cock</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G671" t="str">
         <v>Faucets</v>
@@ -35946,22 +35946,22 @@
         <v/>
       </c>
       <c r="L671" t="str">
-        <v>exposed-parts-for-concealed-stop-cock-1-2-chrome.png</v>
+        <v/>
       </c>
       <c r="M671" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N671" t="str">
         <v/>
       </c>
       <c r="O671" t="str">
-        <v>Chrome</v>
+        <v>Rich Gold</v>
       </c>
       <c r="P671" t="str">
-        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
+        <v>Shower Arm Round in Rich Gold finish</v>
       </c>
       <c r="Q671" t="str">
-        <v>₹1,675</v>
+        <v>₹2,992</v>
       </c>
     </row>
     <row r="672">
@@ -35969,19 +35969,19 @@
         <v>Active</v>
       </c>
       <c r="B672" t="str">
-        <v>1823-40EXP</v>
+        <v>AD-3053-RGLD</v>
       </c>
       <c r="C672" t="str">
-        <v>Cube Prima</v>
+        <v>Allied</v>
       </c>
       <c r="D672" t="str">
-        <v>1823-40EXP</v>
+        <v>AD-3051</v>
       </c>
       <c r="E672" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F672" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G672" t="str">
         <v>Faucets</v>
@@ -35999,22 +35999,22 @@
         <v/>
       </c>
       <c r="L672" t="str">
-        <v>exposed-parts-for-diverter-40mm-chrome.png</v>
+        <v/>
       </c>
       <c r="M672" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N672" t="str">
         <v/>
       </c>
       <c r="O672" t="str">
-        <v>Chrome</v>
+        <v>Rose Gold</v>
       </c>
       <c r="P672" t="str">
-        <v>Exposed Parts For Diverter in Chrome finish</v>
+        <v>Shower Arm Round in Rose Gold finish</v>
       </c>
       <c r="Q672" t="str">
-        <v>₹3,214</v>
+        <v>₹2,992</v>
       </c>
     </row>
     <row r="673">
@@ -36022,19 +36022,19 @@
         <v>Active</v>
       </c>
       <c r="B673" t="str">
-        <v>8022-35EXP</v>
+        <v>AD-3053-GMB</v>
       </c>
       <c r="C673" t="str">
-        <v>Flora</v>
+        <v>Allied</v>
       </c>
       <c r="D673" t="str">
-        <v>8022-35EXP</v>
+        <v>AD-3051</v>
       </c>
       <c r="E673" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F673" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G673" t="str">
         <v>Faucets</v>
@@ -36052,22 +36052,22 @@
         <v/>
       </c>
       <c r="L673" t="str">
-        <v>exposed-parts-for-diverter-35mm-chrome.png</v>
+        <v/>
       </c>
       <c r="M673" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N673" t="str">
         <v/>
       </c>
       <c r="O673" t="str">
-        <v>Chrome</v>
+        <v>Gunmetal Black</v>
       </c>
       <c r="P673" t="str">
-        <v>Exposed Parts For Diverter in Chrome finish</v>
+        <v>Shower Arm Round in Gunmetal Black finish</v>
       </c>
       <c r="Q673" t="str">
-        <v>₹2,630</v>
+        <v>₹1,601</v>
       </c>
     </row>
     <row r="674">
@@ -36075,19 +36075,19 @@
         <v>Active</v>
       </c>
       <c r="B674" t="str">
-        <v>8010-15EXP</v>
+        <v>AD-3053-GMBG</v>
       </c>
       <c r="C674" t="str">
-        <v>Flora</v>
+        <v>Allied</v>
       </c>
       <c r="D674" t="str">
-        <v>8010-15EXP</v>
+        <v>AD-3051</v>
       </c>
       <c r="E674" t="str">
-        <v>exposed-parts-for-concealed-stop-cock</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F674" t="str">
-        <v>Exposed Parts For Concealed Stop Cock</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G674" t="str">
         <v>Faucets</v>
@@ -36105,22 +36105,22 @@
         <v/>
       </c>
       <c r="L674" t="str">
-        <v>exposed-parts-for-concealed-stop-cock-1-2-chrome.png</v>
+        <v/>
       </c>
       <c r="M674" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N674" t="str">
         <v/>
       </c>
       <c r="O674" t="str">
-        <v>Chrome</v>
+        <v>Gunmetal Black Gold</v>
       </c>
       <c r="P674" t="str">
-        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
+        <v>Shower Arm Round in Gunmetal Black Gold finish</v>
       </c>
       <c r="Q674" t="str">
-        <v>₹1,190</v>
+        <v>₹1,782</v>
       </c>
     </row>
     <row r="675">
@@ -36128,19 +36128,19 @@
         <v>Active</v>
       </c>
       <c r="B675" t="str">
-        <v>225-35EXP</v>
+        <v>AD-3053-MB</v>
       </c>
       <c r="C675" t="str">
-        <v>Fuzone</v>
+        <v>Allied</v>
       </c>
       <c r="D675" t="str">
-        <v>225-35EXP</v>
+        <v>AD-3051</v>
       </c>
       <c r="E675" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F675" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G675" t="str">
         <v>Faucets</v>
@@ -36158,22 +36158,22 @@
         <v/>
       </c>
       <c r="L675" t="str">
-        <v>exposed-parts-for-diverter-35mm-chrome.png</v>
+        <v/>
       </c>
       <c r="M675" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N675" t="str">
         <v/>
       </c>
       <c r="O675" t="str">
-        <v>Chrome</v>
+        <v>Matt Black</v>
       </c>
       <c r="P675" t="str">
-        <v>Exposed Parts For Diverter in Chrome finish</v>
+        <v>Shower Arm Round in Matt Black finish</v>
       </c>
       <c r="Q675" t="str">
-        <v>₹2,449</v>
+        <v>₹1,601</v>
       </c>
     </row>
     <row r="676">
@@ -36181,19 +36181,19 @@
         <v>Active</v>
       </c>
       <c r="B676" t="str">
-        <v>209-15EXP</v>
+        <v>AD-3053-MBG</v>
       </c>
       <c r="C676" t="str">
-        <v>Fuzone</v>
+        <v>Allied</v>
       </c>
       <c r="D676" t="str">
-        <v>209-15EXP</v>
+        <v>AD-3051</v>
       </c>
       <c r="E676" t="str">
-        <v>exposed-parts-for-concealed-stop-cock</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F676" t="str">
-        <v>Exposed Parts For Concealed Stop Cock</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G676" t="str">
         <v>Faucets</v>
@@ -36211,22 +36211,22 @@
         <v/>
       </c>
       <c r="L676" t="str">
-        <v>exposed-parts-for-concealed-stop-cock-1-2-chrome.png</v>
+        <v/>
       </c>
       <c r="M676" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N676" t="str">
         <v/>
       </c>
       <c r="O676" t="str">
-        <v>Chrome</v>
+        <v>Matt Black Gold</v>
       </c>
       <c r="P676" t="str">
-        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
+        <v>Shower Arm Round in Matt Black Gold finish</v>
       </c>
       <c r="Q676" t="str">
-        <v>₹1,316</v>
+        <v>₹1,782</v>
       </c>
     </row>
     <row r="677">
@@ -36234,19 +36234,19 @@
         <v>Active</v>
       </c>
       <c r="B677" t="str">
-        <v>187-15EXP</v>
+        <v>AD-3053-MW</v>
       </c>
       <c r="C677" t="str">
-        <v>JP</v>
+        <v>Allied</v>
       </c>
       <c r="D677" t="str">
-        <v>187-15EXP</v>
+        <v>AD-3051</v>
       </c>
       <c r="E677" t="str">
-        <v>exposed-parts-for-concealed-stop-cock</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F677" t="str">
-        <v>Exposed Parts For Concealed Stop Cock</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G677" t="str">
         <v>Faucets</v>
@@ -36264,22 +36264,22 @@
         <v/>
       </c>
       <c r="L677" t="str">
-        <v>exposed-parts-for-concealed-stop-cock-1-2-chrome.png</v>
+        <v/>
       </c>
       <c r="M677" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N677" t="str">
         <v/>
       </c>
       <c r="O677" t="str">
-        <v>Chrome</v>
+        <v>Matt White</v>
       </c>
       <c r="P677" t="str">
-        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
+        <v>Shower Arm Round in Matt White finish</v>
       </c>
       <c r="Q677" t="str">
-        <v>₹1,198</v>
+        <v>₹1,601</v>
       </c>
     </row>
     <row r="678">
@@ -36287,19 +36287,19 @@
         <v>Active</v>
       </c>
       <c r="B678" t="str">
-        <v>1409-15EXP</v>
+        <v>AD-3053-MWG</v>
       </c>
       <c r="C678" t="str">
-        <v>Neo</v>
+        <v>Allied</v>
       </c>
       <c r="D678" t="str">
-        <v>1409-15EXP</v>
+        <v>AD-3051</v>
       </c>
       <c r="E678" t="str">
-        <v>exposed-parts-for-concealed-stop-cock</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F678" t="str">
-        <v>Exposed Parts For Concealed Stop Cock</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G678" t="str">
         <v>Faucets</v>
@@ -36317,22 +36317,22 @@
         <v/>
       </c>
       <c r="L678" t="str">
-        <v>exposed-parts-for-concealed-stop-cock-1-2-chrome.png</v>
+        <v/>
       </c>
       <c r="M678" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N678" t="str">
         <v/>
       </c>
       <c r="O678" t="str">
-        <v>Chrome</v>
+        <v>Matt White Gold</v>
       </c>
       <c r="P678" t="str">
-        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
+        <v>Shower Arm Round in Matt White Gold finish</v>
       </c>
       <c r="Q678" t="str">
-        <v>₹842</v>
+        <v>₹1,782</v>
       </c>
     </row>
     <row r="679">
@@ -36340,19 +36340,19 @@
         <v>Active</v>
       </c>
       <c r="B679" t="str">
-        <v>1423-40EXP</v>
+        <v>AD-3053-MBE</v>
       </c>
       <c r="C679" t="str">
-        <v>Neo</v>
+        <v>Allied</v>
       </c>
       <c r="D679" t="str">
-        <v>1423-40EXP</v>
+        <v>AD-3051</v>
       </c>
       <c r="E679" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F679" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G679" t="str">
         <v>Faucets</v>
@@ -36370,22 +36370,22 @@
         <v/>
       </c>
       <c r="L679" t="str">
-        <v>exposed-parts-for-diverter-40mm-chrome.png</v>
+        <v/>
       </c>
       <c r="M679" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N679" t="str">
         <v/>
       </c>
       <c r="O679" t="str">
-        <v>Chrome</v>
+        <v>Matt Beige</v>
       </c>
       <c r="P679" t="str">
-        <v>Exposed Parts For Diverter in Chrome finish</v>
+        <v>Shower Arm Round in Matt Beige finish</v>
       </c>
       <c r="Q679" t="str">
-        <v>₹2,634</v>
+        <v>₹1,601</v>
       </c>
     </row>
     <row r="680">
@@ -36393,19 +36393,19 @@
         <v>Active</v>
       </c>
       <c r="B680" t="str">
-        <v>1723-35EXP</v>
+        <v>AD-3053-MBEG</v>
       </c>
       <c r="C680" t="str">
-        <v>Opell Prima</v>
+        <v>Allied</v>
       </c>
       <c r="D680" t="str">
-        <v>1723-35EXP</v>
+        <v>AD-3051</v>
       </c>
       <c r="E680" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F680" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G680" t="str">
         <v>Faucets</v>
@@ -36423,22 +36423,22 @@
         <v/>
       </c>
       <c r="L680" t="str">
-        <v>exposed-parts-for-diverter-35mm-chrome.jpg</v>
+        <v/>
       </c>
       <c r="M680" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N680" t="str">
         <v/>
       </c>
       <c r="O680" t="str">
-        <v>Chrome</v>
+        <v>Matt Beige Gold</v>
       </c>
       <c r="P680" t="str">
-        <v>Exposed Parts For Diverter in Chrome finish</v>
+        <v>Shower Arm Round in Matt Beige Gold finish</v>
       </c>
       <c r="Q680" t="str">
-        <v>₹2,770</v>
+        <v>₹1,782</v>
       </c>
     </row>
     <row r="681">
@@ -36446,19 +36446,19 @@
         <v>Active</v>
       </c>
       <c r="B681" t="str">
-        <v>1723-35EXP-GLD</v>
+        <v>AD-3053-MGR</v>
       </c>
       <c r="C681" t="str">
-        <v>Opell Prima</v>
+        <v>Allied</v>
       </c>
       <c r="D681" t="str">
-        <v>1723-35EXP</v>
+        <v>AD-3051</v>
       </c>
       <c r="E681" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F681" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G681" t="str">
         <v>Faucets</v>
@@ -36476,22 +36476,22 @@
         <v/>
       </c>
       <c r="L681" t="str">
-        <v>exposed-parts-for-diverter-35mm-rich-gold.png</v>
+        <v/>
       </c>
       <c r="M681" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N681" t="str">
         <v/>
       </c>
       <c r="O681" t="str">
-        <v>Rich Gold</v>
+        <v>Matt Grey</v>
       </c>
       <c r="P681" t="str">
-        <v>Exposed Parts For Diverter in Rich Gold finish</v>
+        <v>Shower Arm Round in Matt Grey finish</v>
       </c>
       <c r="Q681" t="str">
-        <v/>
+        <v>₹1,601</v>
       </c>
     </row>
     <row r="682">
@@ -36499,19 +36499,19 @@
         <v>Active</v>
       </c>
       <c r="B682" t="str">
-        <v>1723-35EXP-RGLD</v>
+        <v>AD-3053-MGRG</v>
       </c>
       <c r="C682" t="str">
-        <v>Opell Prima</v>
+        <v>Allied</v>
       </c>
       <c r="D682" t="str">
-        <v>1723-35EXP</v>
+        <v>AD-3051</v>
       </c>
       <c r="E682" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>shower-arm-round</v>
       </c>
       <c r="F682" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Shower Arm Round</v>
       </c>
       <c r="G682" t="str">
         <v>Faucets</v>
@@ -36529,22 +36529,22 @@
         <v/>
       </c>
       <c r="L682" t="str">
-        <v>exposed-parts-for-diverter-35mm-rose-gold.png</v>
+        <v/>
       </c>
       <c r="M682" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N682" t="str">
         <v/>
       </c>
       <c r="O682" t="str">
-        <v>Rose Gold</v>
+        <v>Matt Grey Gold</v>
       </c>
       <c r="P682" t="str">
-        <v>Exposed Parts For Diverter in Rose Gold finish</v>
+        <v>Shower Arm Round in Matt Grey Gold finish</v>
       </c>
       <c r="Q682" t="str">
-        <v/>
+        <v>₹1,782</v>
       </c>
     </row>
     <row r="683">
@@ -36552,22 +36552,22 @@
         <v>Active</v>
       </c>
       <c r="B683" t="str">
-        <v>1723-35EXP-GMB</v>
+        <v>AD-3071</v>
       </c>
       <c r="C683" t="str">
-        <v>Opell Prima</v>
+        <v>Allied</v>
       </c>
       <c r="D683" t="str">
-        <v>1723-35EXP</v>
+        <v>AD-3071</v>
       </c>
       <c r="E683" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>ultra-slim-over-head-shower-square</v>
       </c>
       <c r="F683" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Ultra Slim Over Head Shower Square</v>
       </c>
       <c r="G683" t="str">
-        <v>Faucets</v>
+        <v>Shower</v>
       </c>
       <c r="H683" t="str">
         <v/>
@@ -36582,22 +36582,22 @@
         <v/>
       </c>
       <c r="L683" t="str">
-        <v>exposed-parts-for-diverter-35mm-gunmetal-black.png</v>
+        <v/>
       </c>
       <c r="M683" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N683" t="str">
         <v/>
       </c>
       <c r="O683" t="str">
-        <v>Gunmetal Black</v>
+        <v>Chrome</v>
       </c>
       <c r="P683" t="str">
-        <v>Exposed Parts For Diverter in Gunmetal Black finish</v>
+        <v>Ultra Slim Over Head Shower Square in Chrome finish</v>
       </c>
       <c r="Q683" t="str">
-        <v>₹3,601</v>
+        <v>₹625</v>
       </c>
     </row>
     <row r="684">
@@ -36605,19 +36605,19 @@
         <v>Active</v>
       </c>
       <c r="B684" t="str">
-        <v>1723-35EXP-GMBG</v>
+        <v>1810-15EXP</v>
       </c>
       <c r="C684" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="D684" t="str">
-        <v>1723-35EXP</v>
+        <v>1810-15EXP</v>
       </c>
       <c r="E684" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>exposed-parts-for-concealed-stop-cock</v>
       </c>
       <c r="F684" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Exposed Parts For Concealed Stop Cock</v>
       </c>
       <c r="G684" t="str">
         <v>Faucets</v>
@@ -36635,22 +36635,22 @@
         <v/>
       </c>
       <c r="L684" t="str">
-        <v>exposed-parts-for-diverter-35mm-gunmetal-black-gold.png</v>
+        <v/>
       </c>
       <c r="M684" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N684" t="str">
         <v/>
       </c>
       <c r="O684" t="str">
-        <v>Gunmetal Black Gold</v>
+        <v>Chrome</v>
       </c>
       <c r="P684" t="str">
-        <v>Exposed Parts For Diverter in Gunmetal Black Gold finish</v>
+        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
       </c>
       <c r="Q684" t="str">
-        <v/>
+        <v>₹1,675</v>
       </c>
     </row>
     <row r="685">
@@ -36658,13 +36658,13 @@
         <v>Active</v>
       </c>
       <c r="B685" t="str">
-        <v>1723-35EXP-MB</v>
+        <v>1823-40EXP</v>
       </c>
       <c r="C685" t="str">
-        <v>Opell Prima</v>
+        <v>Cube Prima</v>
       </c>
       <c r="D685" t="str">
-        <v>1723-35EXP</v>
+        <v>1823-40EXP</v>
       </c>
       <c r="E685" t="str">
         <v>exposed-parts-for-diverter</v>
@@ -36688,22 +36688,22 @@
         <v/>
       </c>
       <c r="L685" t="str">
-        <v>exposed-parts-for-diverter-35mm-matt-black.png</v>
+        <v/>
       </c>
       <c r="M685" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N685" t="str">
         <v/>
       </c>
       <c r="O685" t="str">
-        <v>Matt Black</v>
+        <v>Chrome</v>
       </c>
       <c r="P685" t="str">
-        <v>Exposed Parts For Diverter in Matt Black finish</v>
+        <v>Exposed Parts For Diverter in Chrome finish</v>
       </c>
       <c r="Q685" t="str">
-        <v>₹3,601</v>
+        <v>₹3,214</v>
       </c>
     </row>
     <row r="686">
@@ -36711,13 +36711,13 @@
         <v>Active</v>
       </c>
       <c r="B686" t="str">
-        <v>1723-35EXP-MBG</v>
+        <v>8022-35EXP</v>
       </c>
       <c r="C686" t="str">
-        <v>Opell Prima</v>
+        <v>Flora</v>
       </c>
       <c r="D686" t="str">
-        <v>1723-35EXP</v>
+        <v>8022-35EXP</v>
       </c>
       <c r="E686" t="str">
         <v>exposed-parts-for-diverter</v>
@@ -36741,22 +36741,22 @@
         <v/>
       </c>
       <c r="L686" t="str">
-        <v>exposed-parts-for-diverter-35mm-matt-black-gold.png</v>
+        <v/>
       </c>
       <c r="M686" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N686" t="str">
         <v/>
       </c>
       <c r="O686" t="str">
-        <v>Matt Black Gold</v>
+        <v>Chrome</v>
       </c>
       <c r="P686" t="str">
-        <v>Exposed Parts For Diverter in Matt Black Gold finish</v>
+        <v>Exposed Parts For Diverter in Chrome finish</v>
       </c>
       <c r="Q686" t="str">
-        <v/>
+        <v>₹2,630</v>
       </c>
     </row>
     <row r="687">
@@ -36764,19 +36764,19 @@
         <v>Active</v>
       </c>
       <c r="B687" t="str">
-        <v>1723-35EXP-MW</v>
+        <v>8010-15EXP</v>
       </c>
       <c r="C687" t="str">
-        <v>Opell Prima</v>
+        <v>Flora</v>
       </c>
       <c r="D687" t="str">
-        <v>1723-35EXP</v>
+        <v>8010-15EXP</v>
       </c>
       <c r="E687" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>exposed-parts-for-concealed-stop-cock</v>
       </c>
       <c r="F687" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Exposed Parts For Concealed Stop Cock</v>
       </c>
       <c r="G687" t="str">
         <v>Faucets</v>
@@ -36794,22 +36794,22 @@
         <v/>
       </c>
       <c r="L687" t="str">
-        <v>exposed-parts-for-diverter-35mm-matt-white.png</v>
+        <v/>
       </c>
       <c r="M687" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N687" t="str">
         <v/>
       </c>
       <c r="O687" t="str">
-        <v>Matt White</v>
+        <v>Chrome</v>
       </c>
       <c r="P687" t="str">
-        <v>Exposed Parts For Diverter in Matt White finish</v>
+        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
       </c>
       <c r="Q687" t="str">
-        <v>₹3,601</v>
+        <v>₹1,190</v>
       </c>
     </row>
     <row r="688">
@@ -36817,13 +36817,13 @@
         <v>Active</v>
       </c>
       <c r="B688" t="str">
-        <v>1723-35EXP-MWG</v>
+        <v>225-35EXP</v>
       </c>
       <c r="C688" t="str">
-        <v>Opell Prima</v>
+        <v>Fuzone</v>
       </c>
       <c r="D688" t="str">
-        <v>1723-35EXP</v>
+        <v>225-35EXP</v>
       </c>
       <c r="E688" t="str">
         <v>exposed-parts-for-diverter</v>
@@ -36847,22 +36847,22 @@
         <v/>
       </c>
       <c r="L688" t="str">
-        <v>exposed-parts-for-diverter-35mm-matt-white-gold.png</v>
+        <v/>
       </c>
       <c r="M688" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N688" t="str">
         <v/>
       </c>
       <c r="O688" t="str">
-        <v>Matt White Gold</v>
+        <v>Chrome</v>
       </c>
       <c r="P688" t="str">
-        <v>Exposed Parts For Diverter in Matt White Gold finish</v>
+        <v>Exposed Parts For Diverter in Chrome finish</v>
       </c>
       <c r="Q688" t="str">
-        <v/>
+        <v>₹2,449</v>
       </c>
     </row>
     <row r="689">
@@ -36870,19 +36870,19 @@
         <v>Active</v>
       </c>
       <c r="B689" t="str">
-        <v>1723-35EXP-MBE</v>
+        <v>209-15EXP</v>
       </c>
       <c r="C689" t="str">
-        <v>Opell Prima</v>
+        <v>Fuzone</v>
       </c>
       <c r="D689" t="str">
-        <v>1723-35EXP</v>
+        <v>209-15EXP</v>
       </c>
       <c r="E689" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>exposed-parts-for-concealed-stop-cock</v>
       </c>
       <c r="F689" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Exposed Parts For Concealed Stop Cock</v>
       </c>
       <c r="G689" t="str">
         <v>Faucets</v>
@@ -36900,22 +36900,22 @@
         <v/>
       </c>
       <c r="L689" t="str">
-        <v>exposed-parts-for-diverter-35mm-matt-beige.png</v>
+        <v/>
       </c>
       <c r="M689" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N689" t="str">
         <v/>
       </c>
       <c r="O689" t="str">
-        <v>Matt Beige</v>
+        <v>Chrome</v>
       </c>
       <c r="P689" t="str">
-        <v>Exposed Parts For Diverter in Matt Beige finish</v>
+        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
       </c>
       <c r="Q689" t="str">
-        <v>₹3,601</v>
+        <v>₹1,316</v>
       </c>
     </row>
     <row r="690">
@@ -36923,19 +36923,19 @@
         <v>Active</v>
       </c>
       <c r="B690" t="str">
-        <v>1723-35EXP-MBEG</v>
+        <v>187-15EXP</v>
       </c>
       <c r="C690" t="str">
-        <v>Opell Prima</v>
+        <v>JP</v>
       </c>
       <c r="D690" t="str">
-        <v>1723-35EXP</v>
+        <v>187-15EXP</v>
       </c>
       <c r="E690" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>exposed-parts-for-concealed-stop-cock</v>
       </c>
       <c r="F690" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Exposed Parts For Concealed Stop Cock</v>
       </c>
       <c r="G690" t="str">
         <v>Faucets</v>
@@ -36953,22 +36953,22 @@
         <v/>
       </c>
       <c r="L690" t="str">
-        <v>exposed-parts-for-diverter-35mm-matt-beige-gold.png</v>
+        <v/>
       </c>
       <c r="M690" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N690" t="str">
         <v/>
       </c>
       <c r="O690" t="str">
-        <v>Matt Beige Gold</v>
+        <v>Chrome</v>
       </c>
       <c r="P690" t="str">
-        <v>Exposed Parts For Diverter in Matt Beige Gold finish</v>
+        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
       </c>
       <c r="Q690" t="str">
-        <v/>
+        <v>₹1,198</v>
       </c>
     </row>
     <row r="691">
@@ -36976,19 +36976,19 @@
         <v>Active</v>
       </c>
       <c r="B691" t="str">
-        <v>1723-35EXP-MGR</v>
+        <v>1409-15EXP</v>
       </c>
       <c r="C691" t="str">
-        <v>Opell Prima</v>
+        <v>Neo</v>
       </c>
       <c r="D691" t="str">
-        <v>1723-35EXP</v>
+        <v>1409-15EXP</v>
       </c>
       <c r="E691" t="str">
-        <v>exposed-parts-for-diverter</v>
+        <v>exposed-parts-for-concealed-stop-cock</v>
       </c>
       <c r="F691" t="str">
-        <v>Exposed Parts For Diverter</v>
+        <v>Exposed Parts For Concealed Stop Cock</v>
       </c>
       <c r="G691" t="str">
         <v>Faucets</v>
@@ -37006,22 +37006,22 @@
         <v/>
       </c>
       <c r="L691" t="str">
-        <v>exposed-parts-for-diverter-35mm-matt-grey.png</v>
+        <v/>
       </c>
       <c r="M691" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N691" t="str">
         <v/>
       </c>
       <c r="O691" t="str">
-        <v>Matt Grey</v>
+        <v>Chrome</v>
       </c>
       <c r="P691" t="str">
-        <v>Exposed Parts For Diverter in Matt Grey finish</v>
+        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
       </c>
       <c r="Q691" t="str">
-        <v>₹3,601</v>
+        <v>₹842</v>
       </c>
     </row>
     <row r="692">
@@ -37029,13 +37029,13 @@
         <v>Active</v>
       </c>
       <c r="B692" t="str">
-        <v>1723-35EXP-MGRG</v>
+        <v>1423-40EXP</v>
       </c>
       <c r="C692" t="str">
-        <v>Opell Prima</v>
+        <v>Neo</v>
       </c>
       <c r="D692" t="str">
-        <v>1723-35EXP</v>
+        <v>1423-40EXP</v>
       </c>
       <c r="E692" t="str">
         <v>exposed-parts-for-diverter</v>
@@ -37062,19 +37062,19 @@
         <v/>
       </c>
       <c r="M692" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N692" t="str">
         <v/>
       </c>
       <c r="O692" t="str">
-        <v>Matt Grey Gold</v>
+        <v>Chrome</v>
       </c>
       <c r="P692" t="str">
-        <v>Exposed Parts For Diverter in Matt Grey Gold finish</v>
+        <v>Exposed Parts For Diverter in Chrome finish</v>
       </c>
       <c r="Q692" t="str">
-        <v/>
+        <v>₹2,634</v>
       </c>
     </row>
     <row r="693">
@@ -37082,19 +37082,19 @@
         <v>Active</v>
       </c>
       <c r="B693" t="str">
-        <v>1710-15EXP</v>
+        <v>1723-35EXP</v>
       </c>
       <c r="C693" t="str">
         <v>Opell Prima</v>
       </c>
       <c r="D693" t="str">
-        <v>1710-15EXP</v>
+        <v>1723-35EXP</v>
       </c>
       <c r="E693" t="str">
-        <v>exposed-parts-for-concealed-stop-cock</v>
+        <v>exposed-parts-for-diverter</v>
       </c>
       <c r="F693" t="str">
-        <v>Exposed Parts For Concealed Stop Cock</v>
+        <v>Exposed Parts For Diverter</v>
       </c>
       <c r="G693" t="str">
         <v>Faucets</v>
@@ -37112,10 +37112,10 @@
         <v/>
       </c>
       <c r="L693" t="str">
-        <v>exposed-parts-for-concealed-stop-cock-1-2-chrome.jpg</v>
+        <v/>
       </c>
       <c r="M693" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N693" t="str">
         <v/>
@@ -37124,10 +37124,10 @@
         <v>Chrome</v>
       </c>
       <c r="P693" t="str">
-        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
+        <v>Exposed Parts For Diverter in Chrome finish</v>
       </c>
       <c r="Q693" t="str">
-        <v>₹1,417</v>
+        <v>₹2,770</v>
       </c>
     </row>
     <row r="694">
@@ -37135,13 +37135,13 @@
         <v>Active</v>
       </c>
       <c r="B694" t="str">
-        <v>1923-35EXP</v>
+        <v>1723-35EXP-GLD</v>
       </c>
       <c r="C694" t="str">
-        <v>Para</v>
+        <v>Opell Prima</v>
       </c>
       <c r="D694" t="str">
-        <v>1923-35EXP</v>
+        <v>1723-35EXP</v>
       </c>
       <c r="E694" t="str">
         <v>exposed-parts-for-diverter</v>
@@ -37165,22 +37165,22 @@
         <v/>
       </c>
       <c r="L694" t="str">
-        <v>exposed-parts-for-diverter-35mm-chrome.png</v>
+        <v/>
       </c>
       <c r="M694" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N694" t="str">
         <v/>
       </c>
       <c r="O694" t="str">
-        <v>Chrome</v>
+        <v>Rich Gold</v>
       </c>
       <c r="P694" t="str">
-        <v>Exposed Parts For Diverter in Chrome finish</v>
+        <v>Exposed Parts For Diverter in Rich Gold finish</v>
       </c>
       <c r="Q694" t="str">
-        <v>₹3,056</v>
+        <v/>
       </c>
     </row>
     <row r="695">
@@ -37188,13 +37188,13 @@
         <v>Active</v>
       </c>
       <c r="B695" t="str">
-        <v>423-35EXP</v>
+        <v>1723-35EXP-RGLD</v>
       </c>
       <c r="C695" t="str">
-        <v>Pebble</v>
+        <v>Opell Prima</v>
       </c>
       <c r="D695" t="str">
-        <v>423-35EXP</v>
+        <v>1723-35EXP</v>
       </c>
       <c r="E695" t="str">
         <v>exposed-parts-for-diverter</v>
@@ -37218,22 +37218,22 @@
         <v/>
       </c>
       <c r="L695" t="str">
-        <v>exposed-parts-for-diverter-35mm-chrome.png</v>
+        <v/>
       </c>
       <c r="M695" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N695" t="str">
         <v/>
       </c>
       <c r="O695" t="str">
-        <v>Chrome</v>
+        <v>Rose Gold</v>
       </c>
       <c r="P695" t="str">
-        <v>Exposed Parts For Diverter in Chrome finish</v>
+        <v>Exposed Parts For Diverter in Rose Gold finish</v>
       </c>
       <c r="Q695" t="str">
-        <v>₹2,553</v>
+        <v/>
       </c>
     </row>
     <row r="696">
@@ -37241,19 +37241,19 @@
         <v>Active</v>
       </c>
       <c r="B696" t="str">
-        <v>408-15EXP</v>
+        <v>1723-35EXP-GMB</v>
       </c>
       <c r="C696" t="str">
-        <v>Pebble</v>
+        <v>Opell Prima</v>
       </c>
       <c r="D696" t="str">
-        <v>408-15EXP</v>
+        <v>1723-35EXP</v>
       </c>
       <c r="E696" t="str">
-        <v>exposed-parts-for-concealed-stop-cock</v>
+        <v>exposed-parts-for-diverter</v>
       </c>
       <c r="F696" t="str">
-        <v>Exposed Parts For Concealed Stop Cock</v>
+        <v>Exposed Parts For Diverter</v>
       </c>
       <c r="G696" t="str">
         <v>Faucets</v>
@@ -37271,22 +37271,22 @@
         <v/>
       </c>
       <c r="L696" t="str">
-        <v>exposed-parts-for-concealed-stop-cock-1-2-chrome.jpg</v>
+        <v/>
       </c>
       <c r="M696" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N696" t="str">
         <v/>
       </c>
       <c r="O696" t="str">
-        <v>Chrome</v>
+        <v>Gunmetal Black</v>
       </c>
       <c r="P696" t="str">
-        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
+        <v>Exposed Parts For Diverter in Gunmetal Black finish</v>
       </c>
       <c r="Q696" t="str">
-        <v>₹1,210</v>
+        <v>₹3,601</v>
       </c>
     </row>
     <row r="697">
@@ -37294,13 +37294,13 @@
         <v>Active</v>
       </c>
       <c r="B697" t="str">
-        <v>9023-35EXP</v>
+        <v>1723-35EXP-GMBG</v>
       </c>
       <c r="C697" t="str">
-        <v>Zenith</v>
+        <v>Opell Prima</v>
       </c>
       <c r="D697" t="str">
-        <v>9023-35EXP</v>
+        <v>1723-35EXP</v>
       </c>
       <c r="E697" t="str">
         <v>exposed-parts-for-diverter</v>
@@ -37324,19 +37324,19 @@
         <v/>
       </c>
       <c r="L697" t="str">
-        <v>exposed-parts-for-diverter-35mm-chrome.png</v>
+        <v/>
       </c>
       <c r="M697" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N697" t="str">
         <v/>
       </c>
       <c r="O697" t="str">
-        <v>Chrome</v>
+        <v>Gunmetal Black Gold</v>
       </c>
       <c r="P697" t="str">
-        <v>Exposed Parts For Diverter in Chrome finish</v>
+        <v>Exposed Parts For Diverter in Gunmetal Black Gold finish</v>
       </c>
       <c r="Q697" t="str">
         <v/>
@@ -37347,13 +37347,13 @@
         <v>Active</v>
       </c>
       <c r="B698" t="str">
-        <v>9023-35EXP-GMB</v>
+        <v>1723-35EXP-MB</v>
       </c>
       <c r="C698" t="str">
-        <v>Zenith</v>
+        <v>Opell Prima</v>
       </c>
       <c r="D698" t="str">
-        <v>9023-35EXP</v>
+        <v>1723-35EXP</v>
       </c>
       <c r="E698" t="str">
         <v>exposed-parts-for-diverter</v>
@@ -37377,34 +37377,723 @@
         <v/>
       </c>
       <c r="L698" t="str">
-        <v>exposed-parts-for-diverter-35mm-gunmetal-black.png</v>
+        <v/>
       </c>
       <c r="M698" t="str">
-        <v/>
+        <v>yes</v>
       </c>
       <c r="N698" t="str">
         <v/>
       </c>
       <c r="O698" t="str">
+        <v>Matt Black</v>
+      </c>
+      <c r="P698" t="str">
+        <v>Exposed Parts For Diverter in Matt Black finish</v>
+      </c>
+      <c r="Q698" t="str">
+        <v>₹3,601</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B699" t="str">
+        <v>1723-35EXP-MBG</v>
+      </c>
+      <c r="C699" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="D699" t="str">
+        <v>1723-35EXP</v>
+      </c>
+      <c r="E699" t="str">
+        <v>exposed-parts-for-diverter</v>
+      </c>
+      <c r="F699" t="str">
+        <v>Exposed Parts For Diverter</v>
+      </c>
+      <c r="G699" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H699" t="str">
+        <v/>
+      </c>
+      <c r="I699" t="str">
+        <v/>
+      </c>
+      <c r="J699" t="str">
+        <v/>
+      </c>
+      <c r="K699" t="str">
+        <v/>
+      </c>
+      <c r="L699" t="str">
+        <v/>
+      </c>
+      <c r="M699" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N699" t="str">
+        <v/>
+      </c>
+      <c r="O699" t="str">
+        <v>Matt Black Gold</v>
+      </c>
+      <c r="P699" t="str">
+        <v>Exposed Parts For Diverter in Matt Black Gold finish</v>
+      </c>
+      <c r="Q699" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B700" t="str">
+        <v>1723-35EXP-MW</v>
+      </c>
+      <c r="C700" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="D700" t="str">
+        <v>1723-35EXP</v>
+      </c>
+      <c r="E700" t="str">
+        <v>exposed-parts-for-diverter</v>
+      </c>
+      <c r="F700" t="str">
+        <v>Exposed Parts For Diverter</v>
+      </c>
+      <c r="G700" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H700" t="str">
+        <v/>
+      </c>
+      <c r="I700" t="str">
+        <v/>
+      </c>
+      <c r="J700" t="str">
+        <v/>
+      </c>
+      <c r="K700" t="str">
+        <v/>
+      </c>
+      <c r="L700" t="str">
+        <v/>
+      </c>
+      <c r="M700" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N700" t="str">
+        <v/>
+      </c>
+      <c r="O700" t="str">
+        <v>Matt White</v>
+      </c>
+      <c r="P700" t="str">
+        <v>Exposed Parts For Diverter in Matt White finish</v>
+      </c>
+      <c r="Q700" t="str">
+        <v>₹3,601</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B701" t="str">
+        <v>1723-35EXP-MWG</v>
+      </c>
+      <c r="C701" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="D701" t="str">
+        <v>1723-35EXP</v>
+      </c>
+      <c r="E701" t="str">
+        <v>exposed-parts-for-diverter</v>
+      </c>
+      <c r="F701" t="str">
+        <v>Exposed Parts For Diverter</v>
+      </c>
+      <c r="G701" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H701" t="str">
+        <v/>
+      </c>
+      <c r="I701" t="str">
+        <v/>
+      </c>
+      <c r="J701" t="str">
+        <v/>
+      </c>
+      <c r="K701" t="str">
+        <v/>
+      </c>
+      <c r="L701" t="str">
+        <v/>
+      </c>
+      <c r="M701" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N701" t="str">
+        <v/>
+      </c>
+      <c r="O701" t="str">
+        <v>Matt White Gold</v>
+      </c>
+      <c r="P701" t="str">
+        <v>Exposed Parts For Diverter in Matt White Gold finish</v>
+      </c>
+      <c r="Q701" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B702" t="str">
+        <v>1723-35EXP-MBE</v>
+      </c>
+      <c r="C702" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="D702" t="str">
+        <v>1723-35EXP</v>
+      </c>
+      <c r="E702" t="str">
+        <v>exposed-parts-for-diverter</v>
+      </c>
+      <c r="F702" t="str">
+        <v>Exposed Parts For Diverter</v>
+      </c>
+      <c r="G702" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H702" t="str">
+        <v/>
+      </c>
+      <c r="I702" t="str">
+        <v/>
+      </c>
+      <c r="J702" t="str">
+        <v/>
+      </c>
+      <c r="K702" t="str">
+        <v/>
+      </c>
+      <c r="L702" t="str">
+        <v/>
+      </c>
+      <c r="M702" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N702" t="str">
+        <v/>
+      </c>
+      <c r="O702" t="str">
+        <v>Matt Beige</v>
+      </c>
+      <c r="P702" t="str">
+        <v>Exposed Parts For Diverter in Matt Beige finish</v>
+      </c>
+      <c r="Q702" t="str">
+        <v>₹3,601</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B703" t="str">
+        <v>1723-35EXP-MBEG</v>
+      </c>
+      <c r="C703" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="D703" t="str">
+        <v>1723-35EXP</v>
+      </c>
+      <c r="E703" t="str">
+        <v>exposed-parts-for-diverter</v>
+      </c>
+      <c r="F703" t="str">
+        <v>Exposed Parts For Diverter</v>
+      </c>
+      <c r="G703" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H703" t="str">
+        <v/>
+      </c>
+      <c r="I703" t="str">
+        <v/>
+      </c>
+      <c r="J703" t="str">
+        <v/>
+      </c>
+      <c r="K703" t="str">
+        <v/>
+      </c>
+      <c r="L703" t="str">
+        <v/>
+      </c>
+      <c r="M703" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N703" t="str">
+        <v/>
+      </c>
+      <c r="O703" t="str">
+        <v>Matt Beige Gold</v>
+      </c>
+      <c r="P703" t="str">
+        <v>Exposed Parts For Diverter in Matt Beige Gold finish</v>
+      </c>
+      <c r="Q703" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B704" t="str">
+        <v>1723-35EXP-MGR</v>
+      </c>
+      <c r="C704" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="D704" t="str">
+        <v>1723-35EXP</v>
+      </c>
+      <c r="E704" t="str">
+        <v>exposed-parts-for-diverter</v>
+      </c>
+      <c r="F704" t="str">
+        <v>Exposed Parts For Diverter</v>
+      </c>
+      <c r="G704" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H704" t="str">
+        <v/>
+      </c>
+      <c r="I704" t="str">
+        <v/>
+      </c>
+      <c r="J704" t="str">
+        <v/>
+      </c>
+      <c r="K704" t="str">
+        <v/>
+      </c>
+      <c r="L704" t="str">
+        <v/>
+      </c>
+      <c r="M704" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N704" t="str">
+        <v/>
+      </c>
+      <c r="O704" t="str">
+        <v>Matt Grey</v>
+      </c>
+      <c r="P704" t="str">
+        <v>Exposed Parts For Diverter in Matt Grey finish</v>
+      </c>
+      <c r="Q704" t="str">
+        <v>₹3,601</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B705" t="str">
+        <v>1723-35EXP-MGRG</v>
+      </c>
+      <c r="C705" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="D705" t="str">
+        <v>1723-35EXP</v>
+      </c>
+      <c r="E705" t="str">
+        <v>exposed-parts-for-diverter</v>
+      </c>
+      <c r="F705" t="str">
+        <v>Exposed Parts For Diverter</v>
+      </c>
+      <c r="G705" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H705" t="str">
+        <v/>
+      </c>
+      <c r="I705" t="str">
+        <v/>
+      </c>
+      <c r="J705" t="str">
+        <v/>
+      </c>
+      <c r="K705" t="str">
+        <v/>
+      </c>
+      <c r="L705" t="str">
+        <v/>
+      </c>
+      <c r="M705" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N705" t="str">
+        <v/>
+      </c>
+      <c r="O705" t="str">
+        <v>Matt Grey Gold</v>
+      </c>
+      <c r="P705" t="str">
+        <v>Exposed Parts For Diverter in Matt Grey Gold finish</v>
+      </c>
+      <c r="Q705" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B706" t="str">
+        <v>1710-15EXP</v>
+      </c>
+      <c r="C706" t="str">
+        <v>Opell Prima</v>
+      </c>
+      <c r="D706" t="str">
+        <v>1710-15EXP</v>
+      </c>
+      <c r="E706" t="str">
+        <v>exposed-parts-for-concealed-stop-cock</v>
+      </c>
+      <c r="F706" t="str">
+        <v>Exposed Parts For Concealed Stop Cock</v>
+      </c>
+      <c r="G706" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H706" t="str">
+        <v/>
+      </c>
+      <c r="I706" t="str">
+        <v/>
+      </c>
+      <c r="J706" t="str">
+        <v/>
+      </c>
+      <c r="K706" t="str">
+        <v/>
+      </c>
+      <c r="L706" t="str">
+        <v/>
+      </c>
+      <c r="M706" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N706" t="str">
+        <v/>
+      </c>
+      <c r="O706" t="str">
+        <v>Chrome</v>
+      </c>
+      <c r="P706" t="str">
+        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
+      </c>
+      <c r="Q706" t="str">
+        <v>₹1,417</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B707" t="str">
+        <v>1923-35EXP</v>
+      </c>
+      <c r="C707" t="str">
+        <v>Para</v>
+      </c>
+      <c r="D707" t="str">
+        <v>1923-35EXP</v>
+      </c>
+      <c r="E707" t="str">
+        <v>exposed-parts-for-diverter</v>
+      </c>
+      <c r="F707" t="str">
+        <v>Exposed Parts For Diverter</v>
+      </c>
+      <c r="G707" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H707" t="str">
+        <v/>
+      </c>
+      <c r="I707" t="str">
+        <v/>
+      </c>
+      <c r="J707" t="str">
+        <v/>
+      </c>
+      <c r="K707" t="str">
+        <v/>
+      </c>
+      <c r="L707" t="str">
+        <v/>
+      </c>
+      <c r="M707" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N707" t="str">
+        <v/>
+      </c>
+      <c r="O707" t="str">
+        <v>Chrome</v>
+      </c>
+      <c r="P707" t="str">
+        <v>Exposed Parts For Diverter in Chrome finish</v>
+      </c>
+      <c r="Q707" t="str">
+        <v>₹3,056</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B708" t="str">
+        <v>423-35EXP</v>
+      </c>
+      <c r="C708" t="str">
+        <v>Pebble</v>
+      </c>
+      <c r="D708" t="str">
+        <v>423-35EXP</v>
+      </c>
+      <c r="E708" t="str">
+        <v>exposed-parts-for-diverter</v>
+      </c>
+      <c r="F708" t="str">
+        <v>Exposed Parts For Diverter</v>
+      </c>
+      <c r="G708" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H708" t="str">
+        <v/>
+      </c>
+      <c r="I708" t="str">
+        <v/>
+      </c>
+      <c r="J708" t="str">
+        <v/>
+      </c>
+      <c r="K708" t="str">
+        <v/>
+      </c>
+      <c r="L708" t="str">
+        <v/>
+      </c>
+      <c r="M708" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N708" t="str">
+        <v/>
+      </c>
+      <c r="O708" t="str">
+        <v>Chrome</v>
+      </c>
+      <c r="P708" t="str">
+        <v>Exposed Parts For Diverter in Chrome finish</v>
+      </c>
+      <c r="Q708" t="str">
+        <v>₹2,553</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B709" t="str">
+        <v>408-15EXP</v>
+      </c>
+      <c r="C709" t="str">
+        <v>Pebble</v>
+      </c>
+      <c r="D709" t="str">
+        <v>408-15EXP</v>
+      </c>
+      <c r="E709" t="str">
+        <v>exposed-parts-for-concealed-stop-cock</v>
+      </c>
+      <c r="F709" t="str">
+        <v>Exposed Parts For Concealed Stop Cock</v>
+      </c>
+      <c r="G709" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H709" t="str">
+        <v/>
+      </c>
+      <c r="I709" t="str">
+        <v/>
+      </c>
+      <c r="J709" t="str">
+        <v/>
+      </c>
+      <c r="K709" t="str">
+        <v/>
+      </c>
+      <c r="L709" t="str">
+        <v/>
+      </c>
+      <c r="M709" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N709" t="str">
+        <v/>
+      </c>
+      <c r="O709" t="str">
+        <v>Chrome</v>
+      </c>
+      <c r="P709" t="str">
+        <v>Exposed Parts For Concealed Stop Cock in Chrome finish</v>
+      </c>
+      <c r="Q709" t="str">
+        <v>₹1,210</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B710" t="str">
+        <v>9023-35EXP</v>
+      </c>
+      <c r="C710" t="str">
+        <v>Zenith</v>
+      </c>
+      <c r="D710" t="str">
+        <v>9023-35EXP</v>
+      </c>
+      <c r="E710" t="str">
+        <v>exposed-parts-for-diverter</v>
+      </c>
+      <c r="F710" t="str">
+        <v>Exposed Parts For Diverter</v>
+      </c>
+      <c r="G710" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H710" t="str">
+        <v/>
+      </c>
+      <c r="I710" t="str">
+        <v/>
+      </c>
+      <c r="J710" t="str">
+        <v/>
+      </c>
+      <c r="K710" t="str">
+        <v/>
+      </c>
+      <c r="L710" t="str">
+        <v/>
+      </c>
+      <c r="M710" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N710" t="str">
+        <v/>
+      </c>
+      <c r="O710" t="str">
+        <v>Chrome</v>
+      </c>
+      <c r="P710" t="str">
+        <v>Exposed Parts For Diverter in Chrome finish</v>
+      </c>
+      <c r="Q710" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="str">
+        <v>Active</v>
+      </c>
+      <c r="B711" t="str">
+        <v>9023-35EXP-GMB</v>
+      </c>
+      <c r="C711" t="str">
+        <v>Zenith</v>
+      </c>
+      <c r="D711" t="str">
+        <v>9023-35EXP</v>
+      </c>
+      <c r="E711" t="str">
+        <v>exposed-parts-for-diverter</v>
+      </c>
+      <c r="F711" t="str">
+        <v>Exposed Parts For Diverter</v>
+      </c>
+      <c r="G711" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="H711" t="str">
+        <v/>
+      </c>
+      <c r="I711" t="str">
+        <v/>
+      </c>
+      <c r="J711" t="str">
+        <v/>
+      </c>
+      <c r="K711" t="str">
+        <v/>
+      </c>
+      <c r="L711" t="str">
+        <v/>
+      </c>
+      <c r="M711" t="str">
+        <v>yes</v>
+      </c>
+      <c r="N711" t="str">
+        <v/>
+      </c>
+      <c r="O711" t="str">
         <v>Gunmetal Black</v>
       </c>
-      <c r="P698" t="str">
+      <c r="P711" t="str">
         <v>Exposed Parts For Diverter in Gunmetal Black finish</v>
       </c>
-      <c r="Q698" t="str">
+      <c r="Q711" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q698"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q711"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -37814,36 +38503,123 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
+        <v>Single Piece Wc</v>
+      </c>
+      <c r="B15" t="str">
+        <v>single-piece-wc</v>
+      </c>
+      <c r="C15" t="str">
+        <v>7 designs · 1 finish</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
         <v>Bathroom Accessories</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B16" t="str">
         <v>bathroom-accessories</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C16" t="str">
         <v>6 designs · 13 finishes</v>
       </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v>Faucets</v>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v>Faucets</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Basin With Pedestal</v>
+      </c>
+      <c r="B17" t="str">
+        <v>basin-with-pedestal</v>
+      </c>
+      <c r="C17" t="str">
+        <v>4 designs · 1 finish</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Wall Hung Wc</v>
+      </c>
+      <c r="B18" t="str">
+        <v>wall-hung-wc</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2 designs · 1 finish</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v>Sanitaryware</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I18"/>
   </ignoredErrors>
 </worksheet>
 </file>
